--- a/Config/Datas/Tables/g_关卡_StageConfig.xlsx
+++ b/Config/Datas/Tables/g_关卡_StageConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStage" sheetId="1" r:id="R2de36e5ef17a4e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbStage" sheetId="1" r:id="R7f96669543614eea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -720,6 +720,12 @@
       <x:c r="J1" s="58" t="str">
         <x:v>initialSkillIds</x:v>
       </x:c>
+      <x:c r="K1" t="str">
+        <x:v>runBuildId</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>tribulationSliceId</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="61" t="str">
@@ -751,6 +757,12 @@
       </x:c>
       <x:c r="J2" s="61" t="str">
         <x:v>(list#sep=;),int#ref=TbSkill</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>int?#ref=TbRunBuild</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>int?#ref=TbTribulationSlice</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -766,6 +778,7 @@
       <x:c r="H3" s="66"/>
       <x:c r="I3" s="66"/>
       <x:c r="J3" s="66"/>
+      <x:c r="K3"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="69" t="str">
@@ -798,6 +811,12 @@
       <x:c r="J4" s="70" t="str">
         <x:v>初始技能列表</x:v>
       </x:c>
+      <x:c r="K4" t="str">
+        <x:v>局内构筑方案；空仅用于既有兼容入口</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>可选借劫炼器切片配置</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="50"/>
@@ -827,6 +846,83 @@
       </x:c>
       <x:c r="J5" s="50" t="str">
         <x:v>20001</x:v>
+      </x:c>
+      <x:c r="K5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>借劫炼器·磐岳</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>10101</x:v>
+      </x:c>
+      <x:c r="J6" t="inlineStr">
+        <x:is>
+          <x:t>20043;20001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="L6" t="n">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>借劫炼器·周天</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>10201</x:v>
+      </x:c>
+      <x:c r="J7" t="inlineStr">
+        <x:is>
+          <x:t>20033;20014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="L7" t="n">
+        <x:v>102</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
